--- a/SeleniumProject/TestData/SearchData.xlsx
+++ b/SeleniumProject/TestData/SearchData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\source\repos\SeleniumProject\SeleniumProject\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39C45449-21E8-4824-9CAB-4C38FDE6120F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EFC7331-BE53-461A-AC1E-1F7A77F74EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{8E8B9928-0A8B-44D1-B53D-2BFCB0E0603C}"/>
+    <workbookView xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{8E8B9928-0A8B-44D1-B53D-2BFCB0E0603C}"/>
   </bookViews>
   <sheets>
     <sheet name="SearchData" sheetId="1" r:id="rId1"/>
@@ -56,24 +56,6 @@
     <t>Run</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-SEARCH-001 </t>
-  </si>
-  <si>
-    <t>TC-SEARCH-002</t>
-  </si>
-  <si>
-    <t>TC-SEARCH-003</t>
-  </si>
-  <si>
-    <t>TC-SEARCH-004</t>
-  </si>
-  <si>
-    <t>TC-SEARCH-005</t>
-  </si>
-  <si>
-    <t>TC-SEARCH-006</t>
-  </si>
-  <si>
     <t>left</t>
   </si>
   <si>
@@ -108,6 +90,24 @@
   </si>
   <si>
     <t>Sort</t>
+  </si>
+  <si>
+    <t>TC-SFS-001</t>
+  </si>
+  <si>
+    <t>TC-SFS-003</t>
+  </si>
+  <si>
+    <t>TC-SFS-004</t>
+  </si>
+  <si>
+    <t>TC-SFS-005</t>
+  </si>
+  <si>
+    <t>TC-SFS-006</t>
+  </si>
+  <si>
+    <t>TC-SFS-007</t>
   </si>
 </sst>
 </file>
@@ -511,13 +511,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
         <v>5</v>
@@ -525,92 +525,92 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>200000</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
